--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/JUNTA EMBREAGEM.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/JUNTA EMBREAGEM.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JUNTA EMB VEDAMOTORS YBR125/ CRUX YD100 2011 A 2017</t>
+          <t>JUNTA EMBREAGEM VEDAMOTORS YBR125/ CRUX YD100 2011 A 2017</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +457,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JUNTA EMB VEDAMOTORS CG TITAN FAN150 2004/ CRF 150F 2012/ BROS NXR150 2006/ CG125 2009</t>
+          <t>JUNTA EMBREAGEM VEDAMOTORS CG TITAN FAN150 2004/ CRF 150F 2012/ BROS NXR150 2006/ CG125 2009</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -478,7 +482,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -491,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JUNTA EMB VEDAMOTORS CBX250 TWISTER/ TORNADO XR250/ CB300/ XRE300</t>
+          <t>JUNTA EMBREAGEM VEDAMOTORS CBX250 TWISTER/ TORNADO XR250/ CB300/ XRE300</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -499,7 +507,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -512,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JUNTA EMB VEDAMOTORS CG125 2000/ TITAN 2000 KS/ BROS NXR150 2002 A 2005/ NXR125 2003 A 2005</t>
+          <t>JUNTA EMBREAGEM VEDAMOTORS CG125 2000/ TITAN 2000 KS/ BROS NXR150 2002 A 2005/ NXR125 2003 A 2005</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -520,7 +532,11 @@
           <t>32</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -533,7 +549,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JUNTA EMB VEDAMOTORS YS-250 FAZER</t>
+          <t>JUNTA EMBREAGEM VEDAMOTORS YS-250 FAZER</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -558,7 +574,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JUNTA EMB VEDAMOTORS XT660R</t>
+          <t>JUNTA EMBREAGEM VEDAMOTORS XT660R</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -566,7 +582,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -579,7 +599,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JUNTA EMB VEDAMOTORS BROS NXR160/ TITAN FAN CG160</t>
+          <t>JUNTA EMBREAGEM VEDAMOTORS BROS NXR160/ TITAN FAN CG160</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -589,7 +609,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t> </t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -604,7 +624,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JUNTA EMB VEDAMOTORS BROS NXR160 2016/ CG FAN TITAN160 2016/ XRE190 2016</t>
+          <t>JUNTA EMBREAGEM VEDAMOTORS BROS NXR160 2016/ CG FAN TITAN160 2016/ XRE190 2016</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -612,7 +632,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -625,7 +649,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JUNTA EMB VEDAMOTORS SUSUKI YES125 2005 A 2012/ INTRUDER125 2002/ KATANA 1996 A 2002</t>
+          <t>JUNTA EMBREAGEM VEDAMOTORS SUSUKI YES125 2005 A 2012/ INTRUDER125 2002/ KATANA 1996 A 2002</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -633,7 +657,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -646,7 +674,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUNTA EMB VEDAMOTORS XT660R </t>
+          <t xml:space="preserve">JUNTA EMBREAGEM VEDAMOTORS XT660R </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -654,7 +682,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -667,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JUNTA EMB VALFLEX XRE190</t>
+          <t>JUNTA EMBREAGEM VALFLEX XRE190</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -675,7 +707,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -688,7 +724,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JUNTA EMB VEDAMOTORS FAZER YS150 2014/ FACTOR125I 2017</t>
+          <t>JUNTA EMBREAGEM VEDAMOTORS FAZER YS150 2014/ FACTOR125I 2017</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -696,7 +732,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -709,7 +749,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JUNTA EMB VALFLEX BROS NXR150 2012 A 2015/ CG TITAN FAN125-150 2009 A 2022 56253</t>
+          <t>JUNTA EMBREAGEM VALFLEX BROS NXR150 2012 A 2015/ CG TITAN FAN125-150 2009 A 2022 56253</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -717,7 +757,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -730,7 +774,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JUNTA EMB BRAVIC POP110/ BIZ110 2016 A 2018 BMA4812</t>
+          <t>JUNTA EMBREAGEM BRAVIC POP110/ BIZ110 2016 A 2018 BMA4812</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -738,7 +782,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -751,7 +799,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JUNTA EMB VALFLEX BROS NXR160 2015 A 2022 56433</t>
+          <t>JUNTA EMBREAGEM VALFLEX BROS NXR160 2015 A 2022 56433</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -759,7 +807,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -772,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JUNTA EMB VALFLEX TWISTER CB250 2018 A 2022 56923</t>
+          <t>JUNTA EMBREAGEM VALFLEX TWISTER CB250 2018 A 2022 56923</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -780,7 +832,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -793,7 +849,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JUNTA EMB VALFLEX CBX250 TWISTER/ XR250 TORNADO 56903</t>
+          <t>JUNTA EMBREAGEM VALFLEX CBX250 TWISTER/ XR250 TORNADO 56903</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -818,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JUNTA EMB VEDAMTORS XT660R</t>
+          <t>JUNTA EMBREAGEM VEDAMTORS XT660R</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -826,7 +882,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -839,7 +899,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JUNTA EMB PEÇA+ CB300/ TWISTER/ XRE300</t>
+          <t>JUNTA EMBREAGEM PEÇA+ CB300/ TWISTER/ XRE300</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -864,7 +924,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JUNTA EMB MHX TWISTER CBX250 2001 A 2008/ TORNADO XR250 2001 A 2008/ CB300R 2009 A 2016</t>
+          <t>JUNTA EMBREAGEM MHX TWISTER CBX250 2001 A 2008/ TORNADO XR250 2001 A 2008/ CB300R 2009 A 2016</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -889,7 +949,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JUNTA MAG MHX CB300R 2010 A 2016</t>
+          <t>JUNTA EMBREAGEM MHX CB300R 2010 A 2016</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -914,7 +974,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JUNTA EMB PEÇA+ FAZER250/ LANDER XTZ250</t>
+          <t>JUNTA EMBREAGEM PEÇA+ FAZER250/ LANDER XTZ250</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/JUNTA EMBREAGEM.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/JUNTA EMBREAGEM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>32</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -732,11 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -757,11 +692,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -782,11 +712,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -807,11 +732,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -832,11 +752,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -857,11 +772,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -882,11 +792,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -907,11 +812,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -932,11 +832,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -957,11 +852,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -980,11 +870,6 @@
       <c r="D23" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
     </row>
